--- a/cache/Wildfire/wildfire_runs_payload.xlsx
+++ b/cache/Wildfire/wildfire_runs_payload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnnickDewald\PycharmProjects\DawnDesignTool\cache\Wildfire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4180EEDF-6000-42A9-9B74-5FF537F7DC36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7809A606-5034-48DA-B242-70FE7502E7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="13680" xr2:uid="{5B225A7C-2425-4B12-971A-E195856C5D49}"/>
+    <workbookView xWindow="-28920" yWindow="-3150" windowWidth="29040" windowHeight="15720" xr2:uid="{5B225A7C-2425-4B12-971A-E195856C5D49}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
   <si>
     <t>battery_specific_energy_Wh_kg</t>
   </si>
@@ -62,34 +62,31 @@
     <t>revisit_rate</t>
   </si>
   <si>
-    <t>331.5 Wh/kg battery pack, 26% solar efficiency</t>
-  </si>
-  <si>
     <t>payload_power</t>
   </si>
   <si>
     <t>structural_mass_margin_multiplier</t>
   </si>
   <si>
-    <t>540 Wh/kg battery pack, 28% solar efficiency, 10% struct. margin, 100W payload power</t>
-  </si>
-  <si>
     <t>wing_span</t>
   </si>
   <si>
-    <t>35m wingspan, min alt set by strat height, no alt. cycling, revisit every 12 hours</t>
-  </si>
-  <si>
-    <t>40m wingspan, min alt set by strat height, no alt. cycling, revisit every 12 hours</t>
-  </si>
-  <si>
-    <t>35m wingpsan, min alt set by strat height, no alt. cycling,  every 12 hours</t>
-  </si>
-  <si>
-    <t>405 Wh/kg battery pack, 26% solar efficiency, 10% struct. margin, 100W payload power</t>
-  </si>
-  <si>
-    <t>585 Wh/kg battery pack, 28% solar efficiency, 10% struct. margin, 100W payload power</t>
+    <t>390 Wh/kg battery cell, 25% solar cell efficiency, 10% struct. margin, 100W payload power</t>
+  </si>
+  <si>
+    <t>35m wingpsan, min alt set by strat height, no alt. cycling,  revisit rate 2/day</t>
+  </si>
+  <si>
+    <t>35m wingspan, min alt set by strat height, no alt. cycling,  revisit rate 2/day</t>
+  </si>
+  <si>
+    <t>600 Wh/kg battery cell, 30% solar cell efficiency, 10% struct. margin, 100W payload power</t>
+  </si>
+  <si>
+    <t>450 Wh/kg battery cell, 25% solar cell efficiency, 10% struct. margin, 100W payload power</t>
+  </si>
+  <si>
+    <t>650 Wh/kg battery cell, 30% solar cell efficiency, 10% struct. margin, 100W payload power</t>
   </si>
 </sst>
 </file>
@@ -145,9 +142,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +182,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -291,7 +288,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,7 +430,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -441,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEEA4D99-B955-4859-B9C9-8BD4545DD517}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.109375" customWidth="1"/>
@@ -449,7 +446,7 @@
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" customWidth="1"/>
     <col min="5" max="5" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="75.44140625" customWidth="1"/>
+    <col min="9" max="9" width="78.88671875" customWidth="1"/>
     <col min="10" max="10" width="85" customWidth="1"/>
     <col min="11" max="11" width="76.88671875" customWidth="1"/>
   </cols>
@@ -465,13 +462,13 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" t="s">
         <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -491,7 +488,7 @@
         <v>390</v>
       </c>
       <c r="B2">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -503,7 +500,7 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>1.25</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -512,10 +509,10 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -523,7 +520,7 @@
         <v>600</v>
       </c>
       <c r="B3">
-        <v>0.28000000000000003</v>
+        <v>0.3</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -544,7 +541,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -552,16 +549,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B4">
-        <v>0.28000000000000003</v>
+        <v>0.25</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -570,24 +567,24 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
         <v>6</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="B5">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -602,7 +599,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="s">
         <v>6</v>
@@ -611,38 +608,6 @@
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>650</v>
-      </c>
-      <c r="B6">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>35</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" t="s">
         <v>13</v>
       </c>
     </row>

--- a/cache/Wildfire/wildfire_runs_payload.xlsx
+++ b/cache/Wildfire/wildfire_runs_payload.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnnickDewald\PycharmProjects\DawnDesignTool\cache\Wildfire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7809A606-5034-48DA-B242-70FE7502E7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179F80AC-5633-46F7-AC2F-244D338A1E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-3150" windowWidth="29040" windowHeight="15720" xr2:uid="{5B225A7C-2425-4B12-971A-E195856C5D49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5B225A7C-2425-4B12-971A-E195856C5D49}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -567,7 +567,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="s">
         <v>6</v>
@@ -599,7 +599,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H5" t="s">
         <v>6</v>

--- a/cache/Wildfire/wildfire_runs_payload.xlsx
+++ b/cache/Wildfire/wildfire_runs_payload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnnickDewald\PycharmProjects\DawnDesignTool\cache\Wildfire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179F80AC-5633-46F7-AC2F-244D338A1E30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD38063-834C-49D3-9B53-BBC76827AAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5B225A7C-2425-4B12-971A-E195856C5D49}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>battery_specific_energy_Wh_kg</t>
   </si>
@@ -71,12 +71,6 @@
     <t>wing_span</t>
   </si>
   <si>
-    <t>390 Wh/kg battery cell, 25% solar cell efficiency, 10% struct. margin, 100W payload power</t>
-  </si>
-  <si>
-    <t>35m wingpsan, min alt set by strat height, no alt. cycling,  revisit rate 2/day</t>
-  </si>
-  <si>
     <t>35m wingspan, min alt set by strat height, no alt. cycling,  revisit rate 2/day</t>
   </si>
   <si>
@@ -84,9 +78,6 @@
   </si>
   <si>
     <t>450 Wh/kg battery cell, 25% solar cell efficiency, 10% struct. margin, 100W payload power</t>
-  </si>
-  <si>
-    <t>650 Wh/kg battery cell, 30% solar cell efficiency, 10% struct. margin, 100W payload power</t>
   </si>
 </sst>
 </file>
@@ -438,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEEA4D99-B955-4859-B9C9-8BD4545DD517}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.109375" customWidth="1"/>
@@ -485,10 +476,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>390</v>
+        <v>600</v>
       </c>
       <c r="B2">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -509,18 +500,18 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
         <v>11</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="B3">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -541,74 +532,10 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>450</v>
-      </c>
-      <c r="B4">
-        <v>0.25</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>35</v>
-      </c>
-      <c r="E4">
-        <v>100</v>
-      </c>
-      <c r="F4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>650</v>
-      </c>
-      <c r="B5">
-        <v>0.3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>35</v>
-      </c>
-      <c r="E5">
-        <v>100</v>
-      </c>
-      <c r="F5">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
